--- a/docs/backlog/backlog_v2_4sprints.xlsx
+++ b/docs/backlog/backlog_v2_4sprints.xlsx
@@ -266,7 +266,7 @@
     <t xml:space="preserve">BAJA</t>
   </si>
   <si>
-    <t xml:space="preserve">Depende de US-02 y US-06. Requiere definir el canal de notificación (propuesta: correo + aviso en el sistema).</t>
+    <t xml:space="preserve">Depende de US-02 y US-06. Canal de notificación: aviso en el sistema y correo (decisión D7 de `docs/backlog/reglas-ministerio.md`).</t>
   </si>
   <si>
     <t xml:space="preserve">US-12</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">El pipeline está sano: lint, pruebas, cobertura, Quality Gate y auditoría de dependencias en verde.</t>
   </si>
   <si>
-    <t xml:space="preserve">Checks obligatorios del pull request</t>
+    <t xml:space="preserve">Build de Jenkins del commit en develop (ADR-0008)</t>
   </si>
   <si>
     <t xml:space="preserve">Cobertura ≥ 80 % en código nuevo y ≥ 90 % en el módulo de cálculo, exigida por la herramienta.</t>
@@ -1103,10 +1103,10 @@
     <t xml:space="preserve">coverageThreshold de Jest y Quality Gate</t>
   </si>
   <si>
-    <t xml:space="preserve">El pull request lo aprobó el otro integrante; nadie aprueba su propio código.</t>
+    <t xml:space="preserve">El otro integrante revisó sus commits en develop; nadie aprueba su propio código.</t>
   </si>
   <si>
-    <t xml:space="preserve">Historial del PR en GitHub</t>
+    <t xml:space="preserve">Comentarios de revisión en los commits de GitHub</t>
   </si>
   <si>
     <t xml:space="preserve">Está desplegada en staging y el smoke test pasa con el commit correcto.</t>
@@ -1196,7 +1196,7 @@
     <t xml:space="preserve">Dado un profesor en una materia asignada y un trimestre abierto, cuando registra la nota de una actividad dentro de una dimensión (Ser, Saber, Hacer o Autoevaluación) en la escala de 1 a 100, entonces la nota se guarda y aparece en la planilla.</t>
   </si>
   <si>
-    <t xml:space="preserve">❓ Dado un valor fuera de 1 a 100 [confirmar con el cliente si se admite 0 para actividades no presentadas], vacío o no numérico, cuando intenta guardar, entonces aparece un mensaje junto al campo y no se guarda nada.</t>
+    <t xml:space="preserve">Dado un valor fuera de 1 a 100 (no se admite 0; una actividad no presentada se registra con 1, decisión D1), vacío o no numérico, cuando intenta guardar, entonces aparece un mensaje junto al campo y no se guarda nada.</t>
   </si>
   <si>
     <t xml:space="preserve">M01</t>
@@ -1238,7 +1238,7 @@
     <t xml:space="preserve">RNF-01, R02</t>
   </si>
   <si>
-    <t xml:space="preserve">❓ Dado las notas de los tres trimestres, cuando se calcula la nota anual de la materia, entonces es el promedio de los tres trimestres redondeado al entero [confirmar con el texto del reglamento de evaluación vigente].</t>
+    <t xml:space="preserve">Dado las notas de los tres trimestres, cuando se calcula la nota anual de la materia, entonces es el promedio de los tres trimestres redondeado al entero, 0,5 hacia arriba (decisiones D2 y D3).</t>
   </si>
   <si>
     <t xml:space="preserve">Dado la tabla de casos de prueba firmada por el cliente (semilla en la hoja Reglas MinEdu), cuando corre la suite, entonces el 100 % de los casos da el resultado esperado.</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">M01, R02</t>
   </si>
   <si>
-    <t xml:space="preserve">❓ Dado una dimensión que todavía no tiene actividades con nota, cuando se calcula la nota parcial del trimestre, entonces [definir con el cliente: se muestra como "pendiente" o cuenta como 0].</t>
+    <t xml:space="preserve">Dado una dimensión que todavía no tiene actividades con nota, cuando se calcula la nota parcial del trimestre, entonces la nota trimestral se muestra como "pendiente" e indica qué dimensiones faltan (decisión D4).</t>
   </si>
   <si>
     <t xml:space="preserve">Dado una nota registrada, cuando el profesor la corrige, entonces el sistema exige un motivo y guarda quién la cambió, la fecha y hora, el valor anterior y el nuevo.</t>
@@ -1268,7 +1268,7 @@
     <t xml:space="preserve">Dado una clase de su materia, cuando el profesor marca a cada estudiante como presente, ausente o con licencia, entonces se guarda la asistencia de esa fecha.</t>
   </si>
   <si>
-    <t xml:space="preserve">❓ Dado las asistencias registradas, cuando se calcula el porcentaje, entonces es (presentes [+ licencias, confirmar con el cliente]) / clases dictadas × 100, redondeado a un decimal.</t>
+    <t xml:space="preserve">Dado las asistencias registradas, cuando se calcula el porcentaje, entonces es (presentes + licencias) / clases dictadas × 100, redondeado a un decimal (decisión D5).</t>
   </si>
   <si>
     <t xml:space="preserve">Dado una fecha futura, cuando el profesor intenta registrar asistencia, entonces el sistema lo impide.</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">Dado un curso del profesor, cuando abre el panel, entonces ve a cada estudiante con su promedio actual y su porcentaje de asistencia.</t>
   </si>
   <si>
-    <t xml:space="preserve">❓ Dado un estudiante con promedio menor que 51 o asistencia menor que [umbral a definir con el cliente, p. ej. 80 %], cuando se muestra el panel, entonces aparece marcado como "en riesgo".</t>
+    <t xml:space="preserve">Dado un estudiante con promedio menor que 51 o asistencia menor que 80 % (umbral configurable por gestión, decisión D6), cuando se muestra el panel, entonces aparece marcado como "en riesgo".</t>
   </si>
   <si>
     <t xml:space="preserve">Dado un estudiante, cuando el profesor genera su boletín, entonces el PDF muestra la unidad educativa, el código SIE, el nivel, el año de escolaridad y el paralelo, y por cada materia la nota de cada trimestre, la nota anual y el porcentaje de asistencia, iguales a los que muestra el sistema.</t>
@@ -1376,13 +1376,13 @@
     <t xml:space="preserve">Escala de calificación</t>
   </si>
   <si>
-    <t xml:space="preserve">1 a 100</t>
+    <t xml:space="preserve">1 a 100 (sin 0)</t>
   </si>
   <si>
     <t xml:space="preserve">Ministerio de Educación, vigente desde 2013</t>
   </si>
   <si>
-    <t xml:space="preserve">Confirmar si se admite 0</t>
+    <t xml:space="preserve">Decidido (D1)</t>
   </si>
   <si>
     <t xml:space="preserve">Nota mínima de aprobación</t>
@@ -1415,13 +1415,13 @@
     <t xml:space="preserve">Práctica habitual; no se encontró el texto oficial</t>
   </si>
   <si>
-    <t xml:space="preserve">❓ Confirmar con el reglamento completo</t>
+    <t xml:space="preserve">Decidido (D3)</t>
   </si>
   <si>
     <t xml:space="preserve">Suma de dimensiones (debe ser 100)</t>
   </si>
   <si>
-    <t xml:space="preserve">❓ Confirmar con el cliente</t>
+    <t xml:space="preserve">Confirmado</t>
   </si>
   <si>
     <t xml:space="preserve">Casos de ejemplo del cálculo (semilla de la tabla que firma el cliente, riesgo R02)</t>

--- a/docs/backlog/backlog_v2_4sprints.xlsx
+++ b/docs/backlog/backlog_v2_4sprints.xlsx
@@ -377,7 +377,7 @@
     <t xml:space="preserve">Semana 1. Un profesor inicia sesión, registra notas de su materia y ve el promedio calculado correctamente.</t>
   </si>
   <si>
-    <t xml:space="preserve">Días 1–2: revisión e inspección Fagan del SRS con el cliente; tabla de casos de prueba del cálculo según la RM 001/2026, firmada por el cliente (R02); inspección Fagan del SAD · Día 2: repositorio con develop y main protegidas, Husky y Jenkins Multibranch (ESLint + Prettier, Jest + cobertura, SonarQube Cloud, npm audit) · Día 5: auditoría de cierre del Sprint 1</t>
+    <t xml:space="preserve">Días 1–2: revisión e inspección Fagan del SRS con el cliente; tabla de casos de prueba del cálculo según la RM 001/2026, firmada por el cliente (R02); inspección Fagan del SAD · Día 2: repositorio con develop y main protegidas, Husky y Jenkins Multibranch; staging con despliegue continuo y smoke test (ADR-0009) (ESLint + Prettier, Jest + cobertura, SonarQube Cloud, npm audit) · Día 5: auditoría de cierre del Sprint 1</t>
   </si>
   <si>
     <t xml:space="preserve">US-04, US-03, US-19, US-05, US-10</t>
@@ -386,7 +386,7 @@
     <t xml:space="preserve">Semana 2. Las notas se corrigen con auditoría, se importan desde Excel y se registra la asistencia.</t>
   </si>
   <si>
-    <t xml:space="preserve">Día 1: revisión de diseño detallado de US-04 y US-05 · Staging con despliegue automático y smoke test · Primeros escenarios E2E de Cypress (Registrar calificación) · Día 5: auditoría de cierre del Sprint 2</t>
+    <t xml:space="preserve">Día 1: revisión de diseño detallado de US-04 y US-05 · Primeros escenarios E2E de Cypress (Registrar calificación) · Día 5: auditoría de cierre del Sprint 2</t>
   </si>
   <si>
     <t xml:space="preserve">US-06, US-07, US-20, US-11</t>
@@ -728,7 +728,7 @@
     <t xml:space="preserve">T-028</t>
   </si>
   <si>
-    <t xml:space="preserve">Staging: API en Render, web en Vercel, PostgreSQL administrado; despliegue desde el Jenkinsfile (rama develop) y smoke test del commit desplegado</t>
+    <t xml:space="preserve">Staging con despliegue continuo: API y web en Render (render.yaml, ADR-0009); despliegue desde el Jenkinsfile en cada push a develop y smoke test del commit desplegado</t>
   </si>
   <si>
     <t xml:space="preserve">T-029</t>
@@ -31069,7 +31069,7 @@
       </c>
       <c r="C19" s="22" t="n">
         <f aca="false">SUMIFS('Tareas (Sprint Backlog)'!$H$5:$H$73,'Tareas (Sprint Backlog)'!$B$5:$B$73,A19,'Tareas (Sprint Backlog)'!$F$5:$F$73,"Galvan")</f>
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D19" s="22" t="str">
         <f aca="false">IF(B19&gt;$D$16,"Sobrecarga: "&amp;TEXT(B19-$D$16,"0")&amp;" h","OK")</f>
@@ -31077,7 +31077,7 @@
       </c>
       <c r="E19" s="22" t="str">
         <f aca="false">IF(C19&gt;$D$16,"Sobrecarga: "&amp;TEXT(C19-$D$16,"0")&amp;" h","OK")</f>
-        <v>Sobrecarga: 7 h</v>
+        <v>Sobrecarga: 13 h</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31090,7 +31090,7 @@
       </c>
       <c r="C20" s="22" t="n">
         <f aca="false">SUMIFS('Tareas (Sprint Backlog)'!$H$5:$H$73,'Tareas (Sprint Backlog)'!$B$5:$B$73,A20,'Tareas (Sprint Backlog)'!$F$5:$F$73,"Galvan")</f>
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D20" s="22" t="str">
         <f aca="false">IF(B20&gt;$D$16,"Sobrecarga: "&amp;TEXT(B20-$D$16,"0")&amp;" h","OK")</f>
@@ -32091,7 +32091,7 @@
         <v>231</v>
       </c>
       <c r="B32" s="22" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="C32" s="22" t="s">
         <v>165</v>
@@ -32123,7 +32123,7 @@
         <v>233</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="C33" s="22" t="s">
         <v>165</v>

--- a/docs/backlog/backlog_v2_4sprints.xlsx
+++ b/docs/backlog/backlog_v2_4sprints.xlsx
@@ -2525,8 +2525,10 @@
       <c r="D5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="8" t="s">
-        <v>14</v>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
       </c>
       <c r="F5" s="8" t="n">
         <v>13</v>
@@ -2574,8 +2576,10 @@
       <c r="D6" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="8" t="s">
-        <v>14</v>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
       </c>
       <c r="F6" s="8" t="n">
         <v>13</v>
@@ -2623,8 +2627,10 @@
       <c r="D7" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="11" t="s">
-        <v>14</v>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
       </c>
       <c r="F7" s="11" t="n">
         <v>13</v>
@@ -2672,8 +2678,10 @@
       <c r="D8" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="11" t="s">
-        <v>14</v>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
       </c>
       <c r="F8" s="11" t="n">
         <v>13</v>
@@ -2721,8 +2729,10 @@
       <c r="D9" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="11" t="s">
-        <v>14</v>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
       </c>
       <c r="F9" s="11" t="n">
         <v>8</v>
@@ -2819,8 +2829,10 @@
       <c r="D11" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="8" t="s">
-        <v>14</v>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
       </c>
       <c r="F11" s="8" t="n">
         <v>8</v>
@@ -31281,8 +31293,10 @@
       <c r="H6" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="I6" s="22" t="s">
-        <v>152</v>
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t>En revisión</t>
+        </is>
       </c>
       <c r="J6" s="22" t="s">
         <v>157</v>
@@ -31345,8 +31359,10 @@
       <c r="H8" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="I8" s="22" t="s">
-        <v>152</v>
+      <c r="I8" s="22" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
       </c>
       <c r="J8" s="22" t="s">
         <v>163</v>
@@ -31377,8 +31393,10 @@
       <c r="H9" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="I9" s="22" t="s">
-        <v>152</v>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t>En revisión</t>
+        </is>
       </c>
       <c r="J9" s="22"/>
     </row>
@@ -31407,8 +31425,10 @@
       <c r="H10" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="I10" s="22" t="s">
-        <v>152</v>
+      <c r="I10" s="22" t="inlineStr">
+        <is>
+          <t>En revisión</t>
+        </is>
       </c>
       <c r="J10" s="22" t="s">
         <v>169</v>
@@ -31439,8 +31459,10 @@
       <c r="H11" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="I11" s="22" t="s">
-        <v>152</v>
+      <c r="I11" s="22" t="inlineStr">
+        <is>
+          <t>En revisión</t>
+        </is>
       </c>
       <c r="J11" s="22" t="s">
         <v>172</v>
@@ -31503,8 +31525,10 @@
       <c r="H13" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="I13" s="22" t="s">
-        <v>152</v>
+      <c r="I13" s="22" t="inlineStr">
+        <is>
+          <t>En revisión</t>
+        </is>
       </c>
       <c r="J13" s="22" t="s">
         <v>179</v>
@@ -31535,8 +31559,10 @@
       <c r="H14" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="I14" s="22" t="s">
-        <v>152</v>
+      <c r="I14" s="22" t="inlineStr">
+        <is>
+          <t>En revisión</t>
+        </is>
       </c>
       <c r="J14" s="22" t="s">
         <v>182</v>
@@ -31567,8 +31593,10 @@
       <c r="H15" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="I15" s="22" t="s">
-        <v>152</v>
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t>En revisión</t>
+        </is>
       </c>
       <c r="J15" s="22" t="s">
         <v>185</v>
@@ -31599,8 +31627,10 @@
       <c r="H16" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="I16" s="22" t="s">
-        <v>152</v>
+      <c r="I16" s="22" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
       </c>
       <c r="J16" s="22" t="s">
         <v>189</v>
@@ -31631,8 +31661,10 @@
       <c r="H17" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="I17" s="22" t="s">
-        <v>152</v>
+      <c r="I17" s="22" t="inlineStr">
+        <is>
+          <t>En revisión</t>
+        </is>
       </c>
       <c r="J17" s="22" t="s">
         <v>193</v>
@@ -31663,8 +31695,10 @@
       <c r="H18" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="I18" s="22" t="s">
-        <v>152</v>
+      <c r="I18" s="22" t="inlineStr">
+        <is>
+          <t>En revisión</t>
+        </is>
       </c>
       <c r="J18" s="22" t="s">
         <v>196</v>
@@ -31695,8 +31729,10 @@
       <c r="H19" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="I19" s="26" t="s">
-        <v>152</v>
+      <c r="I19" s="26" t="inlineStr">
+        <is>
+          <t>En revisión</t>
+        </is>
       </c>
       <c r="J19" s="26" t="s">
         <v>200</v>
@@ -31791,8 +31827,10 @@
       <c r="H22" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="I22" s="26" t="s">
-        <v>152</v>
+      <c r="I22" s="26" t="inlineStr">
+        <is>
+          <t>En revisión</t>
+        </is>
       </c>
       <c r="J22" s="26" t="s">
         <v>208</v>
@@ -31823,8 +31861,10 @@
       <c r="H23" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="I23" s="26" t="s">
-        <v>152</v>
+      <c r="I23" s="26" t="inlineStr">
+        <is>
+          <t>En revisión</t>
+        </is>
       </c>
       <c r="J23" s="26" t="s">
         <v>211</v>
@@ -31855,8 +31895,10 @@
       <c r="H24" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="I24" s="22" t="s">
-        <v>152</v>
+      <c r="I24" s="22" t="inlineStr">
+        <is>
+          <t>En revisión</t>
+        </is>
       </c>
       <c r="J24" s="22" t="s">
         <v>211</v>
@@ -31887,8 +31929,10 @@
       <c r="H25" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="I25" s="22" t="s">
-        <v>152</v>
+      <c r="I25" s="22" t="inlineStr">
+        <is>
+          <t>En revisión</t>
+        </is>
       </c>
       <c r="J25" s="22" t="s">
         <v>193</v>
@@ -31919,8 +31963,10 @@
       <c r="H26" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="I26" s="26" t="s">
-        <v>152</v>
+      <c r="I26" s="26" t="inlineStr">
+        <is>
+          <t>En revisión</t>
+        </is>
       </c>
       <c r="J26" s="26" t="s">
         <v>218</v>
@@ -31951,8 +31997,10 @@
       <c r="H27" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="I27" s="22" t="s">
-        <v>152</v>
+      <c r="I27" s="22" t="inlineStr">
+        <is>
+          <t>En revisión</t>
+        </is>
       </c>
       <c r="J27" s="22" t="s">
         <v>221</v>
@@ -32111,8 +32159,10 @@
       <c r="H32" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="I32" s="22" t="s">
-        <v>152</v>
+      <c r="I32" s="22" t="inlineStr">
+        <is>
+          <t>En revisión</t>
+        </is>
       </c>
       <c r="J32" s="22" t="s">
         <v>169</v>
@@ -32143,8 +32193,10 @@
       <c r="H33" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="I33" s="22" t="s">
-        <v>152</v>
+      <c r="I33" s="22" t="inlineStr">
+        <is>
+          <t>En revisión</t>
+        </is>
       </c>
       <c r="J33" s="22" t="s">
         <v>193</v>
@@ -32207,8 +32259,10 @@
       <c r="H35" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="I35" s="26" t="s">
-        <v>152</v>
+      <c r="I35" s="26" t="inlineStr">
+        <is>
+          <t>En revisión</t>
+        </is>
       </c>
       <c r="J35" s="26" t="s">
         <v>240</v>
@@ -32367,8 +32421,10 @@
       <c r="H40" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="I40" s="22" t="s">
-        <v>152</v>
+      <c r="I40" s="22" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
       </c>
       <c r="J40" s="22" t="s">
         <v>252</v>

--- a/docs/backlog/backlog_v2_4sprints.xlsx
+++ b/docs/backlog/backlog_v2_4sprints.xlsx
@@ -32423,7 +32423,7 @@
       </c>
       <c r="I40" s="22" t="inlineStr">
         <is>
-          <t>En proceso</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="J40" s="22" t="s">

--- a/docs/backlog/backlog_v2_4sprints.xlsx
+++ b/docs/backlog/backlog_v2_4sprints.xlsx
@@ -31755,16 +31755,18 @@
         <v>178</v>
       </c>
       <c r="F20" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="G20" s="22" t="s">
         <v>150</v>
-      </c>
-      <c r="G20" s="22" t="s">
-        <v>151</v>
       </c>
       <c r="H20" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="I20" s="22" t="s">
-        <v>152</v>
+      <c r="I20" s="22" t="inlineStr">
+        <is>
+          <t>En revisión</t>
+        </is>
       </c>
       <c r="J20" s="22" t="s">
         <v>203</v>

--- a/docs/backlog/backlog_v2_4sprints.xlsx
+++ b/docs/backlog/backlog_v2_4sprints.xlsx
@@ -31619,10 +31619,10 @@
         <v>188</v>
       </c>
       <c r="F16" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="G16" s="22" t="s">
         <v>150</v>
-      </c>
-      <c r="G16" s="22" t="s">
-        <v>151</v>
       </c>
       <c r="H16" s="22" t="n">
         <v>3</v>
@@ -31653,17 +31653,17 @@
         <v>192</v>
       </c>
       <c r="F17" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="G17" s="22" t="s">
         <v>150</v>
-      </c>
-      <c r="G17" s="22" t="s">
-        <v>151</v>
       </c>
       <c r="H17" s="22" t="n">
         <v>2</v>
       </c>
       <c r="I17" s="22" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>En proceso</t>
         </is>
       </c>
       <c r="J17" s="22" t="s">
@@ -31789,10 +31789,10 @@
         <v>188</v>
       </c>
       <c r="F21" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="G21" s="22" t="s">
         <v>150</v>
-      </c>
-      <c r="G21" s="22" t="s">
-        <v>151</v>
       </c>
       <c r="H21" s="22" t="n">
         <v>4</v>
@@ -31889,17 +31889,17 @@
         <v>188</v>
       </c>
       <c r="F24" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="G24" s="22" t="s">
         <v>150</v>
-      </c>
-      <c r="G24" s="22" t="s">
-        <v>151</v>
       </c>
       <c r="H24" s="22" t="n">
         <v>4</v>
       </c>
       <c r="I24" s="22" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>En proceso</t>
         </is>
       </c>
       <c r="J24" s="22" t="s">
@@ -31923,17 +31923,17 @@
         <v>192</v>
       </c>
       <c r="F25" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="G25" s="22" t="s">
         <v>150</v>
-      </c>
-      <c r="G25" s="22" t="s">
-        <v>151</v>
       </c>
       <c r="H25" s="22" t="n">
         <v>2</v>
       </c>
       <c r="I25" s="22" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>En proceso</t>
         </is>
       </c>
       <c r="J25" s="22" t="s">
@@ -32025,10 +32025,10 @@
         <v>188</v>
       </c>
       <c r="F28" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="G28" s="22" t="s">
         <v>150</v>
-      </c>
-      <c r="G28" s="22" t="s">
-        <v>151</v>
       </c>
       <c r="H28" s="22" t="n">
         <v>2</v>

--- a/docs/backlog/backlog_v2_4sprints.xlsx
+++ b/docs/backlog/backlog_v2_4sprints.xlsx
@@ -31629,7 +31629,7 @@
       </c>
       <c r="I16" s="22" t="inlineStr">
         <is>
-          <t>En proceso</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="J16" s="22" t="s">
@@ -31663,7 +31663,7 @@
       </c>
       <c r="I17" s="22" t="inlineStr">
         <is>
-          <t>En proceso</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="J17" s="22" t="s">
@@ -31797,8 +31797,10 @@
       <c r="H21" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="I21" s="22" t="s">
-        <v>152</v>
+      <c r="I21" s="22" t="inlineStr">
+        <is>
+          <t>En revisión</t>
+        </is>
       </c>
       <c r="J21" s="22" t="s">
         <v>18</v>
@@ -31899,7 +31901,7 @@
       </c>
       <c r="I24" s="22" t="inlineStr">
         <is>
-          <t>En proceso</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="J24" s="22" t="s">
@@ -31933,7 +31935,7 @@
       </c>
       <c r="I25" s="22" t="inlineStr">
         <is>
-          <t>En proceso</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="J25" s="22" t="s">
@@ -32033,8 +32035,10 @@
       <c r="H28" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="I28" s="22" t="s">
-        <v>152</v>
+      <c r="I28" s="22" t="inlineStr">
+        <is>
+          <t>En revisión</t>
+        </is>
       </c>
       <c r="J28" s="22" t="s">
         <v>26</v>

--- a/docs/backlog/backlog_v2_4sprints.xlsx
+++ b/docs/backlog/backlog_v2_4sprints.xlsx
@@ -2780,8 +2780,10 @@
       <c r="D10" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="11" t="s">
-        <v>14</v>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
       </c>
       <c r="F10" s="11" t="n">
         <v>10</v>
@@ -32363,8 +32365,10 @@
       <c r="H38" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="I38" s="22" t="s">
-        <v>152</v>
+      <c r="I38" s="22" t="inlineStr">
+        <is>
+          <t>En revisión</t>
+        </is>
       </c>
       <c r="J38" s="22" t="s">
         <v>247</v>

--- a/docs/backlog/backlog_v2_4sprints.xlsx
+++ b/docs/backlog/backlog_v2_4sprints.xlsx
@@ -2931,8 +2931,10 @@
       <c r="D13" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E13" s="11" t="s">
-        <v>14</v>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
       </c>
       <c r="F13" s="11" t="n">
         <v>5</v>
@@ -32561,8 +32563,10 @@
       <c r="H44" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="I44" s="22" t="s">
-        <v>152</v>
+      <c r="I44" s="22" t="inlineStr">
+        <is>
+          <t>En revisión</t>
+        </is>
       </c>
       <c r="J44" s="22" t="s">
         <v>263</v>

--- a/docs/backlog/backlog_v2_4sprints.xlsx
+++ b/docs/backlog/backlog_v2_4sprints.xlsx
@@ -2882,8 +2882,10 @@
       <c r="D12" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="11" t="s">
-        <v>14</v>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
       </c>
       <c r="F12" s="11" t="n">
         <v>8</v>
@@ -32499,8 +32501,10 @@
       <c r="H42" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="I42" s="26" t="s">
-        <v>152</v>
+      <c r="I42" s="26" t="inlineStr">
+        <is>
+          <t>En revisión</t>
+        </is>
       </c>
       <c r="J42" s="26" t="s">
         <v>257</v>
@@ -32531,8 +32535,10 @@
       <c r="H43" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="I43" s="22" t="s">
-        <v>152</v>
+      <c r="I43" s="22" t="inlineStr">
+        <is>
+          <t>En revisión</t>
+        </is>
       </c>
       <c r="J43" s="22" t="s">
         <v>43</v>

--- a/docs/backlog/backlog_v2_4sprints.xlsx
+++ b/docs/backlog/backlog_v2_4sprints.xlsx
@@ -32305,8 +32305,10 @@
       <c r="H36" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="I36" s="22" t="s">
-        <v>152</v>
+      <c r="I36" s="22" t="inlineStr">
+        <is>
+          <t>En revisión</t>
+        </is>
       </c>
       <c r="J36" s="22" t="s">
         <v>30</v>
@@ -32337,8 +32339,10 @@
       <c r="H37" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="I37" s="22" t="s">
-        <v>152</v>
+      <c r="I37" s="22" t="inlineStr">
+        <is>
+          <t>En revisión</t>
+        </is>
       </c>
       <c r="J37" s="22" t="s">
         <v>193</v>
@@ -32403,8 +32407,10 @@
       <c r="H39" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="I39" s="22" t="s">
-        <v>152</v>
+      <c r="I39" s="22" t="inlineStr">
+        <is>
+          <t>En revisión</t>
+        </is>
       </c>
       <c r="J39" s="22" t="s">
         <v>35</v>
@@ -32469,8 +32475,10 @@
       <c r="H41" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="I41" s="22" t="s">
-        <v>152</v>
+      <c r="I41" s="22" t="inlineStr">
+        <is>
+          <t>En revisión</t>
+        </is>
       </c>
       <c r="J41" s="22" t="s">
         <v>39</v>

--- a/docs/backlog/backlog_v2_4sprints.xlsx
+++ b/docs/backlog/backlog_v2_4sprints.xlsx
@@ -32643,8 +32643,10 @@
       <c r="H46" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="I46" s="22" t="s">
-        <v>152</v>
+      <c r="I46" s="22" t="inlineStr">
+        <is>
+          <t>En revisión</t>
+        </is>
       </c>
       <c r="J46" s="22" t="s">
         <v>153</v>

--- a/docs/backlog/backlog_v2_4sprints.xlsx
+++ b/docs/backlog/backlog_v2_4sprints.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="4"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="574">
   <si>
     <t xml:space="preserve">Desarrollo ágil: Pila de Producto (Product Backlog)</t>
   </si>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Autenticación y Roles</t>
   </si>
   <si>
-    <t xml:space="preserve">Planificada</t>
+    <t xml:space="preserve">En proceso</t>
   </si>
   <si>
     <t xml:space="preserve">Sprint 1</t>
@@ -195,6 +195,9 @@
   </si>
   <si>
     <t xml:space="preserve">Panel de Riesgo Académico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planificada</t>
   </si>
   <si>
     <t xml:space="preserve">Sprint 3</t>
@@ -501,6 +504,9 @@
   </si>
   <si>
     <t xml:space="preserve">Diseño</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En revisión</t>
   </si>
   <si>
     <t xml:space="preserve">SQAP Sec. 4</t>
@@ -927,6 +933,9 @@
   </si>
   <si>
     <t xml:space="preserve">T-056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hecho</t>
   </si>
   <si>
     <t xml:space="preserve">T-057</t>
@@ -1419,9 +1428,6 @@
   </si>
   <si>
     <t xml:space="preserve">Suma de dimensiones (debe ser 100)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confirmado</t>
   </si>
   <si>
     <t xml:space="preserve">Casos de ejemplo del cálculo (semilla de la tabla que firma el cliente, riesgo R02)</t>
@@ -2026,15 +2032,15 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2050,7 +2056,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2066,7 +2072,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2195,37 +2201,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Sheets">
@@ -2365,7 +2371,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="14.4453125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.4453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="1.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.43"/>
@@ -2525,10 +2531,8 @@
       <c r="D5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>En proceso</t>
-        </is>
+      <c r="E5" s="8" t="s">
+        <v>14</v>
       </c>
       <c r="F5" s="8" t="n">
         <v>13</v>
@@ -2576,10 +2580,8 @@
       <c r="D6" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>En proceso</t>
-        </is>
+      <c r="E6" s="8" t="s">
+        <v>14</v>
       </c>
       <c r="F6" s="8" t="n">
         <v>13</v>
@@ -2627,10 +2629,8 @@
       <c r="D7" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>En proceso</t>
-        </is>
+      <c r="E7" s="11" t="s">
+        <v>14</v>
       </c>
       <c r="F7" s="11" t="n">
         <v>13</v>
@@ -2678,10 +2678,8 @@
       <c r="D8" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>En proceso</t>
-        </is>
+      <c r="E8" s="11" t="s">
+        <v>14</v>
       </c>
       <c r="F8" s="11" t="n">
         <v>13</v>
@@ -2729,10 +2727,8 @@
       <c r="D9" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>En proceso</t>
-        </is>
+      <c r="E9" s="11" t="s">
+        <v>14</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>8</v>
@@ -2780,10 +2776,8 @@
       <c r="D10" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>En proceso</t>
-        </is>
+      <c r="E10" s="11" t="s">
+        <v>14</v>
       </c>
       <c r="F10" s="11" t="n">
         <v>10</v>
@@ -2831,10 +2825,8 @@
       <c r="D11" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>En proceso</t>
-        </is>
+      <c r="E11" s="8" t="s">
+        <v>14</v>
       </c>
       <c r="F11" s="8" t="n">
         <v>8</v>
@@ -2882,10 +2874,8 @@
       <c r="D12" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>En proceso</t>
-        </is>
+      <c r="E12" s="11" t="s">
+        <v>14</v>
       </c>
       <c r="F12" s="11" t="n">
         <v>8</v>
@@ -2933,10 +2923,8 @@
       <c r="D13" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>En proceso</t>
-        </is>
+      <c r="E13" s="11" t="s">
+        <v>14</v>
       </c>
       <c r="F13" s="11" t="n">
         <v>5</v>
@@ -2985,7 +2973,7 @@
         <v>54</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="F14" s="11" t="n">
         <v>10</v>
@@ -2998,13 +2986,13 @@
         <v>2</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J14" s="11" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
@@ -3025,16 +3013,16 @@
     <row r="15" customFormat="false" ht="63" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="2"/>
       <c r="B15" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="F15" s="11" t="n">
         <v>13</v>
@@ -3047,13 +3035,13 @@
         <v>1.63</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J15" s="11" t="s">
         <v>46</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
@@ -3074,16 +3062,16 @@
     <row r="16" customFormat="false" ht="63" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="2"/>
       <c r="B16" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="F16" s="8" t="n">
         <v>5</v>
@@ -3096,13 +3084,13 @@
         <v>1.67</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J16" s="8" t="s">
         <v>46</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
@@ -3123,16 +3111,16 @@
     <row r="17" customFormat="false" ht="63" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="2"/>
       <c r="B17" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="F17" s="11" t="n">
         <v>8</v>
@@ -3145,13 +3133,13 @@
         <v>1.6</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J17" s="11" t="s">
         <v>46</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
@@ -3172,16 +3160,16 @@
     <row r="18" customFormat="false" ht="63" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="2"/>
       <c r="B18" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="F18" s="11" t="n">
         <v>8</v>
@@ -3194,13 +3182,13 @@
         <v>1</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J18" s="11" t="s">
         <v>46</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
@@ -3221,16 +3209,16 @@
     <row r="19" customFormat="false" ht="63" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="2"/>
       <c r="B19" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="F19" s="11" t="n">
         <v>8</v>
@@ -3243,13 +3231,13 @@
         <v>1</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
@@ -3270,16 +3258,16 @@
     <row r="20" customFormat="false" ht="63" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="2"/>
       <c r="B20" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="F20" s="11" t="n">
         <v>3</v>
@@ -3292,13 +3280,13 @@
         <v>1.5</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
@@ -3319,13 +3307,13 @@
     <row r="21" customFormat="false" ht="63" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="2"/>
       <c r="B21" s="13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E21" s="14"/>
       <c r="F21" s="14" t="n">
@@ -3339,13 +3327,13 @@
         <v>1.6</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J21" s="14" t="s">
         <v>46</v>
       </c>
       <c r="K21" s="14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
@@ -3366,13 +3354,13 @@
     <row r="22" customFormat="false" ht="63" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="2"/>
       <c r="B22" s="13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E22" s="14"/>
       <c r="F22" s="14" t="n">
@@ -3386,13 +3374,13 @@
         <v>2.67</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J22" s="14" t="s">
         <v>46</v>
       </c>
       <c r="K22" s="14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
@@ -3413,13 +3401,13 @@
     <row r="23" customFormat="false" ht="63" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="2"/>
       <c r="B23" s="13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E23" s="14"/>
       <c r="F23" s="14" t="n">
@@ -3433,13 +3421,13 @@
         <v>1.67</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K23" s="14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
@@ -3460,13 +3448,13 @@
     <row r="24" customFormat="false" ht="63" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="2"/>
       <c r="B24" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E24" s="14"/>
       <c r="F24" s="14" t="n">
@@ -3480,13 +3468,13 @@
         <v>1</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J24" s="14" t="s">
         <v>46</v>
       </c>
       <c r="K24" s="14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
@@ -3535,10 +3523,10 @@
     <row r="26" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="2"/>
       <c r="B26" s="16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
@@ -30853,61 +30841,61 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="70"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D3" s="20" t="n">
         <v>20</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D4" s="20" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30915,7 +30903,7 @@
         <v>15</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C7" s="22" t="n">
         <f aca="false">SUMIFS('Historias de Usuario'!$G$5:$G$24,'Historias de Usuario'!$I$5:$I$24,A7)</f>
@@ -30926,10 +30914,10 @@
         <v>OK</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30937,7 +30925,7 @@
         <v>33</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C8" s="22" t="n">
         <f aca="false">SUMIFS('Historias de Usuario'!$G$5:$G$24,'Historias de Usuario'!$I$5:$I$24,A8)</f>
@@ -30948,18 +30936,18 @@
         <v>OK</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C9" s="22" t="n">
         <f aca="false">SUMIFS('Historias de Usuario'!$G$5:$G$24,'Historias de Usuario'!$I$5:$I$24,A9)</f>
@@ -30970,18 +30958,18 @@
         <v>OK</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C10" s="22" t="n">
         <f aca="false">SUMIFS('Historias de Usuario'!$G$5:$G$24,'Historias de Usuario'!$I$5:$I$24,A10)</f>
@@ -30992,18 +30980,18 @@
         <v>OK</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C11" s="22" t="n">
         <f aca="false">SUMIFS('Historias de Usuario'!$G$5:$G$24,'Historias de Usuario'!$I$5:$I$24,A11)</f>
@@ -31011,15 +30999,15 @@
       </c>
       <c r="D11" s="22"/>
       <c r="E11" s="22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B12" s="23"/>
       <c r="C12" s="23" t="n">
@@ -31033,9 +31021,9 @@
       <c r="E12" s="22"/>
       <c r="F12" s="22"/>
     </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B13" s="23"/>
       <c r="C13" s="23" t="n">
@@ -31049,56 +31037,56 @@
       <c r="E13" s="22"/>
       <c r="F13" s="22"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D16" s="20" t="n">
         <v>30</v>
       </c>
-      <c r="E16" s="0" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E16" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="24" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="22" t="s">
         <v>15</v>
       </c>
       <c r="B19" s="22" t="n">
         <f aca="false">SUMIFS('Tareas (Sprint Backlog)'!$H$5:$H$73,'Tareas (Sprint Backlog)'!$B$5:$B$73,A19,'Tareas (Sprint Backlog)'!$F$5:$F$73,"Lujan")</f>
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="C19" s="22" t="n">
         <f aca="false">SUMIFS('Tareas (Sprint Backlog)'!$H$5:$H$73,'Tareas (Sprint Backlog)'!$B$5:$B$73,A19,'Tareas (Sprint Backlog)'!$F$5:$F$73,"Galvan")</f>
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="D19" s="22" t="str">
         <f aca="false">IF(B19&gt;$D$16,"Sobrecarga: "&amp;TEXT(B19-$D$16,"0")&amp;" h","OK")</f>
-        <v>Sobrecarga: 5 h</v>
+        <v>Sobrecarga: 26 h</v>
       </c>
       <c r="E19" s="22" t="str">
         <f aca="false">IF(C19&gt;$D$16,"Sobrecarga: "&amp;TEXT(C19-$D$16,"0")&amp;" h","OK")</f>
-        <v>Sobrecarga: 13 h</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="22" t="s">
         <v>33</v>
       </c>
@@ -31119,9 +31107,9 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B21" s="22" t="n">
         <f aca="false">SUMIFS('Tareas (Sprint Backlog)'!$H$5:$H$73,'Tareas (Sprint Backlog)'!$B$5:$B$73,A21,'Tareas (Sprint Backlog)'!$F$5:$F$73,"Lujan")</f>
@@ -31140,9 +31128,9 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B22" s="22" t="n">
         <f aca="false">SUMIFS('Tareas (Sprint Backlog)'!$H$5:$H$73,'Tareas (Sprint Backlog)'!$B$5:$B$73,A22,'Tareas (Sprint Backlog)'!$F$5:$F$73,"Lujan")</f>
@@ -31178,27 +31166,27 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J73"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="70"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="20"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="25" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
@@ -31210,305 +31198,295 @@
       <c r="I2" s="25"/>
       <c r="J2" s="25"/>
     </row>
-    <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I4" s="21" t="s">
         <v>4</v>
       </c>
       <c r="J4" s="21" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="22" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B5" s="22" t="s">
         <v>15</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G5" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H5" s="22" t="n">
         <v>3</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J5" s="22" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="22" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B6" s="22" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F6" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G6" s="22" t="s">
         <v>151</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>150</v>
       </c>
       <c r="H6" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="I6" s="22" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
+      <c r="I6" s="22" t="s">
+        <v>158</v>
       </c>
       <c r="J6" s="22" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="22" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B7" s="22" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G7" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H7" s="22" t="n">
         <v>2</v>
       </c>
       <c r="I7" s="22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J7" s="22" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="22" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B8" s="22" t="s">
         <v>15</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F8" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G8" s="22" t="s">
         <v>151</v>
-      </c>
-      <c r="G8" s="22" t="s">
-        <v>150</v>
       </c>
       <c r="H8" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="I8" s="22" t="inlineStr">
-        <is>
-          <t>En proceso</t>
-        </is>
+      <c r="I8" s="22" t="s">
+        <v>14</v>
       </c>
       <c r="J8" s="22" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="22" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B9" s="22" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G9" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H9" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="I9" s="22" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
+      <c r="I9" s="22" t="s">
+        <v>158</v>
       </c>
       <c r="J9" s="22"/>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="22" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B10" s="22" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H10" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="I10" s="22" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
+      <c r="I10" s="22" t="s">
+        <v>158</v>
       </c>
       <c r="J10" s="22" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="22" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B11" s="22" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H11" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="I11" s="22" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
+      <c r="I11" s="22" t="s">
+        <v>158</v>
       </c>
       <c r="J11" s="22" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="22" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B12" s="22" t="s">
         <v>15</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H12" s="22" t="n">
         <v>1</v>
       </c>
       <c r="I12" s="22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J12" s="22" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="22" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B13" s="22" t="s">
         <v>15</v>
@@ -31517,32 +31495,30 @@
         <v>11</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F13" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G13" s="22" t="s">
         <v>151</v>
-      </c>
-      <c r="G13" s="22" t="s">
-        <v>150</v>
       </c>
       <c r="H13" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="I13" s="22" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
+      <c r="I13" s="22" t="s">
+        <v>158</v>
       </c>
       <c r="J13" s="22" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="22" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B14" s="22" t="s">
         <v>15</v>
@@ -31551,32 +31527,30 @@
         <v>11</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F14" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G14" s="22" t="s">
         <v>151</v>
-      </c>
-      <c r="G14" s="22" t="s">
-        <v>150</v>
       </c>
       <c r="H14" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="I14" s="22" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
+      <c r="I14" s="22" t="s">
+        <v>158</v>
       </c>
       <c r="J14" s="22" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="22" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B15" s="22" t="s">
         <v>15</v>
@@ -31585,32 +31559,30 @@
         <v>11</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F15" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G15" s="22" t="s">
         <v>151</v>
-      </c>
-      <c r="G15" s="22" t="s">
-        <v>150</v>
       </c>
       <c r="H15" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="I15" s="22" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
+      <c r="I15" s="22" t="s">
+        <v>158</v>
       </c>
       <c r="J15" s="22" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="22" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>15</v>
@@ -31619,32 +31591,30 @@
         <v>11</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F16" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G16" s="22" t="s">
         <v>151</v>
-      </c>
-      <c r="G16" s="22" t="s">
-        <v>150</v>
       </c>
       <c r="H16" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="I16" s="22" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
+      <c r="I16" s="22" t="s">
+        <v>158</v>
       </c>
       <c r="J16" s="22" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="22" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B17" s="22" t="s">
         <v>15</v>
@@ -31653,32 +31623,30 @@
         <v>11</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F17" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G17" s="22" t="s">
         <v>151</v>
-      </c>
-      <c r="G17" s="22" t="s">
-        <v>150</v>
       </c>
       <c r="H17" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="I17" s="22" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
+      <c r="I17" s="22" t="s">
+        <v>158</v>
       </c>
       <c r="J17" s="22" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="22" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B18" s="22" t="s">
         <v>15</v>
@@ -31687,32 +31655,30 @@
         <v>18</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E18" s="22" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F18" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G18" s="22" t="s">
         <v>151</v>
-      </c>
-      <c r="G18" s="22" t="s">
-        <v>150</v>
       </c>
       <c r="H18" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="I18" s="22" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
+      <c r="I18" s="22" t="s">
+        <v>158</v>
       </c>
       <c r="J18" s="22" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="26" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B19" s="26" t="s">
         <v>15</v>
@@ -31721,32 +31687,30 @@
         <v>18</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F19" s="26" t="s">
+        <v>152</v>
+      </c>
+      <c r="G19" s="26" t="s">
         <v>151</v>
-      </c>
-      <c r="G19" s="26" t="s">
-        <v>150</v>
       </c>
       <c r="H19" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="I19" s="26" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
+      <c r="I19" s="26" t="s">
+        <v>158</v>
       </c>
       <c r="J19" s="26" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="22" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B20" s="22" t="s">
         <v>15</v>
@@ -31755,32 +31719,30 @@
         <v>18</v>
       </c>
       <c r="D20" s="22" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E20" s="22" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F20" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G20" s="22" t="s">
         <v>151</v>
-      </c>
-      <c r="G20" s="22" t="s">
-        <v>150</v>
       </c>
       <c r="H20" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="I20" s="22" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
+      <c r="I20" s="22" t="s">
+        <v>158</v>
       </c>
       <c r="J20" s="22" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="22" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B21" s="22" t="s">
         <v>15</v>
@@ -31789,24 +31751,22 @@
         <v>18</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F21" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G21" s="22" t="s">
         <v>151</v>
-      </c>
-      <c r="G21" s="22" t="s">
-        <v>150</v>
       </c>
       <c r="H21" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="I21" s="22" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
+      <c r="I21" s="22" t="s">
+        <v>158</v>
       </c>
       <c r="J21" s="22" t="s">
         <v>18</v>
@@ -31814,7 +31774,7 @@
     </row>
     <row r="22" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="26" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B22" s="26" t="s">
         <v>15</v>
@@ -31823,32 +31783,30 @@
         <v>22</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E22" s="26" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F22" s="26" t="s">
+        <v>152</v>
+      </c>
+      <c r="G22" s="26" t="s">
         <v>151</v>
-      </c>
-      <c r="G22" s="26" t="s">
-        <v>150</v>
       </c>
       <c r="H22" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="I22" s="26" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
+      <c r="I22" s="26" t="s">
+        <v>158</v>
       </c>
       <c r="J22" s="26" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="26" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B23" s="26" t="s">
         <v>15</v>
@@ -31857,32 +31815,30 @@
         <v>22</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F23" s="26" t="s">
+        <v>152</v>
+      </c>
+      <c r="G23" s="26" t="s">
         <v>151</v>
-      </c>
-      <c r="G23" s="26" t="s">
-        <v>150</v>
       </c>
       <c r="H23" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="I23" s="26" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
+      <c r="I23" s="26" t="s">
+        <v>158</v>
       </c>
       <c r="J23" s="26" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="22" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B24" s="22" t="s">
         <v>15</v>
@@ -31891,32 +31847,30 @@
         <v>22</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E24" s="22" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F24" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G24" s="22" t="s">
         <v>151</v>
-      </c>
-      <c r="G24" s="22" t="s">
-        <v>150</v>
       </c>
       <c r="H24" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="I24" s="22" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
+      <c r="I24" s="22" t="s">
+        <v>158</v>
       </c>
       <c r="J24" s="22" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="22" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B25" s="22" t="s">
         <v>15</v>
@@ -31925,32 +31879,30 @@
         <v>22</v>
       </c>
       <c r="D25" s="22" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E25" s="22" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F25" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G25" s="22" t="s">
         <v>151</v>
-      </c>
-      <c r="G25" s="22" t="s">
-        <v>150</v>
       </c>
       <c r="H25" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="I25" s="22" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
+      <c r="I25" s="22" t="s">
+        <v>158</v>
       </c>
       <c r="J25" s="22" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="26" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B26" s="26" t="s">
         <v>15</v>
@@ -31959,32 +31911,30 @@
         <v>26</v>
       </c>
       <c r="D26" s="26" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E26" s="26" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F26" s="26" t="s">
+        <v>152</v>
+      </c>
+      <c r="G26" s="26" t="s">
         <v>151</v>
-      </c>
-      <c r="G26" s="26" t="s">
-        <v>150</v>
       </c>
       <c r="H26" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="I26" s="26" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
+      <c r="I26" s="26" t="s">
+        <v>158</v>
       </c>
       <c r="J26" s="26" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="22" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B27" s="22" t="s">
         <v>15</v>
@@ -31993,32 +31943,30 @@
         <v>26</v>
       </c>
       <c r="D27" s="22" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F27" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G27" s="22" t="s">
         <v>151</v>
-      </c>
-      <c r="G27" s="22" t="s">
-        <v>150</v>
       </c>
       <c r="H27" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="I27" s="22" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
+      <c r="I27" s="22" t="s">
+        <v>158</v>
       </c>
       <c r="J27" s="22" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="22" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B28" s="22" t="s">
         <v>15</v>
@@ -32027,24 +31975,22 @@
         <v>26</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F28" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G28" s="22" t="s">
         <v>151</v>
-      </c>
-      <c r="G28" s="22" t="s">
-        <v>150</v>
       </c>
       <c r="H28" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="I28" s="22" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
+      <c r="I28" s="22" t="s">
+        <v>158</v>
       </c>
       <c r="J28" s="22" t="s">
         <v>26</v>
@@ -32052,203 +31998,199 @@
     </row>
     <row r="29" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="22" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B29" s="22" t="s">
         <v>15</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D29" s="22" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F29" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G29" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H29" s="22" t="n">
         <v>1</v>
       </c>
       <c r="I29" s="22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J29" s="22" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="22" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B30" s="22" t="s">
         <v>15</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D30" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="E30" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="E30" s="22" t="s">
-        <v>226</v>
-      </c>
       <c r="F30" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G30" s="22" t="s">
         <v>151</v>
-      </c>
-      <c r="G30" s="22" t="s">
-        <v>150</v>
       </c>
       <c r="H30" s="22" t="n">
         <v>1</v>
       </c>
       <c r="I30" s="22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J30" s="22" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="22" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B31" s="22" t="s">
         <v>33</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D31" s="22" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E31" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F31" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G31" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H31" s="22" t="n">
         <v>1</v>
       </c>
       <c r="I31" s="22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J31" s="22" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="22" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B32" s="22" t="s">
         <v>15</v>
       </c>
       <c r="C32" s="22" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D32" s="22" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E32" s="22" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F32" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G32" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H32" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="I32" s="22" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
+      <c r="I32" s="22" t="s">
+        <v>158</v>
       </c>
       <c r="J32" s="22" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="22" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B33" s="22" t="s">
         <v>15</v>
       </c>
       <c r="C33" s="22" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D33" s="22" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E33" s="22" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F33" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G33" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H33" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="I33" s="22" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
+      <c r="I33" s="22" t="s">
+        <v>158</v>
       </c>
       <c r="J33" s="22" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="22" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B34" s="22" t="s">
         <v>33</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D34" s="22" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E34" s="22" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F34" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G34" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H34" s="22" t="n">
         <v>2</v>
       </c>
       <c r="I34" s="22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J34" s="22" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="26" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B35" s="26" t="s">
         <v>33</v>
@@ -32257,32 +32199,30 @@
         <v>30</v>
       </c>
       <c r="D35" s="26" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E35" s="26" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F35" s="26" t="s">
+        <v>152</v>
+      </c>
+      <c r="G35" s="26" t="s">
         <v>151</v>
-      </c>
-      <c r="G35" s="26" t="s">
-        <v>150</v>
       </c>
       <c r="H35" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="I35" s="26" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
+      <c r="I35" s="26" t="s">
+        <v>158</v>
       </c>
       <c r="J35" s="26" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="22" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B36" s="22" t="s">
         <v>33</v>
@@ -32291,24 +32231,22 @@
         <v>30</v>
       </c>
       <c r="D36" s="22" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E36" s="22" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F36" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G36" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H36" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="I36" s="22" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
+      <c r="I36" s="22" t="s">
+        <v>158</v>
       </c>
       <c r="J36" s="22" t="s">
         <v>30</v>
@@ -32316,7 +32254,7 @@
     </row>
     <row r="37" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="22" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B37" s="22" t="s">
         <v>33</v>
@@ -32325,32 +32263,30 @@
         <v>30</v>
       </c>
       <c r="D37" s="22" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E37" s="22" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F37" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G37" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H37" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="I37" s="22" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
+      <c r="I37" s="22" t="s">
+        <v>158</v>
       </c>
       <c r="J37" s="22" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="22" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B38" s="22" t="s">
         <v>33</v>
@@ -32359,32 +32295,30 @@
         <v>35</v>
       </c>
       <c r="D38" s="22" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E38" s="22" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F38" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G38" s="22" t="s">
         <v>151</v>
-      </c>
-      <c r="G38" s="22" t="s">
-        <v>150</v>
       </c>
       <c r="H38" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="I38" s="22" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
+      <c r="I38" s="22" t="s">
+        <v>158</v>
       </c>
       <c r="J38" s="22" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="22" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B39" s="22" t="s">
         <v>33</v>
@@ -32393,24 +32327,22 @@
         <v>35</v>
       </c>
       <c r="D39" s="22" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E39" s="22" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F39" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G39" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H39" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="I39" s="22" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
+      <c r="I39" s="22" t="s">
+        <v>158</v>
       </c>
       <c r="J39" s="22" t="s">
         <v>35</v>
@@ -32418,7 +32350,7 @@
     </row>
     <row r="40" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="22" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B40" s="22" t="s">
         <v>33</v>
@@ -32427,32 +32359,30 @@
         <v>39</v>
       </c>
       <c r="D40" s="22" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E40" s="22" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F40" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G40" s="22" t="s">
         <v>151</v>
-      </c>
-      <c r="G40" s="22" t="s">
-        <v>150</v>
       </c>
       <c r="H40" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="I40" s="22" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
+      <c r="I40" s="22" t="s">
+        <v>158</v>
       </c>
       <c r="J40" s="22" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="22" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B41" s="22" t="s">
         <v>33</v>
@@ -32461,24 +32391,22 @@
         <v>39</v>
       </c>
       <c r="D41" s="22" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E41" s="22" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F41" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G41" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H41" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="I41" s="22" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
+      <c r="I41" s="22" t="s">
+        <v>158</v>
       </c>
       <c r="J41" s="22" t="s">
         <v>39</v>
@@ -32486,7 +32414,7 @@
     </row>
     <row r="42" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="26" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B42" s="26" t="s">
         <v>33</v>
@@ -32495,32 +32423,30 @@
         <v>43</v>
       </c>
       <c r="D42" s="26" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E42" s="26" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F42" s="26" t="s">
+        <v>152</v>
+      </c>
+      <c r="G42" s="26" t="s">
         <v>151</v>
-      </c>
-      <c r="G42" s="26" t="s">
-        <v>150</v>
       </c>
       <c r="H42" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="I42" s="26" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
+      <c r="I42" s="26" t="s">
+        <v>158</v>
       </c>
       <c r="J42" s="26" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="22" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B43" s="22" t="s">
         <v>33</v>
@@ -32529,24 +32455,22 @@
         <v>43</v>
       </c>
       <c r="D43" s="22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F43" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G43" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H43" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="I43" s="22" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
+      <c r="I43" s="22" t="s">
+        <v>158</v>
       </c>
       <c r="J43" s="22" t="s">
         <v>43</v>
@@ -32554,7 +32478,7 @@
     </row>
     <row r="44" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="22" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B44" s="22" t="s">
         <v>33</v>
@@ -32563,154 +32487,150 @@
         <v>48</v>
       </c>
       <c r="D44" s="22" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E44" s="22" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F44" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G44" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H44" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="I44" s="22" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
+      <c r="I44" s="22" t="s">
+        <v>158</v>
       </c>
       <c r="J44" s="22" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="22" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B45" s="22" t="s">
         <v>33</v>
       </c>
       <c r="C45" s="22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D45" s="22" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F45" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G45" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H45" s="22" t="n">
         <v>1</v>
       </c>
       <c r="I45" s="22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J45" s="22" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="22" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B46" s="22" t="s">
         <v>33</v>
       </c>
       <c r="C46" s="22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D46" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="E46" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="E46" s="22" t="s">
-        <v>226</v>
-      </c>
       <c r="F46" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G46" s="22" t="s">
         <v>151</v>
-      </c>
-      <c r="G46" s="22" t="s">
-        <v>150</v>
       </c>
       <c r="H46" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="I46" s="22" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
+      <c r="I46" s="22" t="s">
+        <v>158</v>
       </c>
       <c r="J46" s="22" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="22" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B47" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C47" s="22" t="s">
         <v>52</v>
       </c>
       <c r="D47" s="22" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E47" s="22" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F47" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G47" s="22" t="s">
         <v>151</v>
-      </c>
-      <c r="G47" s="22" t="s">
-        <v>150</v>
       </c>
       <c r="H47" s="22" t="n">
         <v>3</v>
       </c>
       <c r="I47" s="22" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="J47" s="22" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="22" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B48" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C48" s="22" t="s">
         <v>52</v>
       </c>
       <c r="D48" s="22" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E48" s="22" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F48" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G48" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H48" s="22" t="n">
         <v>3</v>
       </c>
       <c r="I48" s="22" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="J48" s="22" t="s">
         <v>52</v>
@@ -32718,802 +32638,802 @@
     </row>
     <row r="49" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="22" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B49" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D49" s="22" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E49" s="22" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F49" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G49" s="22" t="s">
         <v>151</v>
-      </c>
-      <c r="G49" s="22" t="s">
-        <v>150</v>
       </c>
       <c r="H49" s="22" t="n">
         <v>5</v>
       </c>
       <c r="I49" s="22" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="J49" s="22" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="22" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B50" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C50" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D50" s="22" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E50" s="22" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F50" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G50" s="22" t="s">
         <v>151</v>
-      </c>
-      <c r="G50" s="22" t="s">
-        <v>150</v>
       </c>
       <c r="H50" s="22" t="n">
         <v>4</v>
       </c>
       <c r="I50" s="22" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="J50" s="22" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="22" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B51" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C51" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D51" s="22" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E51" s="22" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F51" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G51" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H51" s="22" t="n">
         <v>2</v>
       </c>
       <c r="I51" s="22" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="J51" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="22" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B52" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D52" s="22" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E52" s="22" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F52" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G52" s="22" t="s">
         <v>151</v>
-      </c>
-      <c r="G52" s="22" t="s">
-        <v>150</v>
       </c>
       <c r="H52" s="22" t="n">
         <v>3</v>
       </c>
       <c r="I52" s="22" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="J52" s="22" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="22" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B53" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C53" s="22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D53" s="22" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E53" s="22" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F53" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G53" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H53" s="22" t="n">
         <v>2</v>
       </c>
       <c r="I53" s="22" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="J53" s="22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="22" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B54" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C54" s="22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D54" s="22" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E54" s="22" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F54" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G54" s="22" t="s">
         <v>151</v>
-      </c>
-      <c r="G54" s="22" t="s">
-        <v>150</v>
       </c>
       <c r="H54" s="22" t="n">
         <v>2</v>
       </c>
       <c r="I54" s="22" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="J54" s="22" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="22" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B55" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C55" s="22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D55" s="22" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E55" s="22" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F55" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G55" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H55" s="22" t="n">
         <v>3</v>
       </c>
       <c r="I55" s="22" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="J55" s="22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="22" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B56" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C56" s="22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D56" s="22" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E56" s="22" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F56" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G56" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H56" s="22" t="n">
         <v>3</v>
       </c>
       <c r="I56" s="22" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="J56" s="22" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="22" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B57" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C57" s="22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D57" s="22" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E57" s="22" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F57" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G57" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H57" s="22" t="n">
         <v>3</v>
       </c>
       <c r="I57" s="22" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="J57" s="22" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="22" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B58" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C58" s="22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D58" s="22" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E58" s="22" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F58" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G58" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H58" s="22" t="n">
         <v>3</v>
       </c>
       <c r="I58" s="22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J58" s="22" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="22" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B59" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C59" s="22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D59" s="22" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E59" s="22" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F59" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G59" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H59" s="22" t="n">
         <v>1</v>
       </c>
       <c r="I59" s="22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J59" s="22" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="22" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B60" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C60" s="22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D60" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="E60" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="E60" s="22" t="s">
-        <v>226</v>
-      </c>
       <c r="F60" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G60" s="22" t="s">
         <v>151</v>
-      </c>
-      <c r="G60" s="22" t="s">
-        <v>150</v>
       </c>
       <c r="H60" s="22" t="n">
         <v>1</v>
       </c>
       <c r="I60" s="22" t="s">
-        <v>152</v>
+        <v>301</v>
       </c>
       <c r="J60" s="22" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="22" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B61" s="22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C61" s="22" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D61" s="22" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="E61" s="22" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F61" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G61" s="22" t="s">
         <v>151</v>
-      </c>
-      <c r="G61" s="22" t="s">
-        <v>150</v>
       </c>
       <c r="H61" s="22" t="n">
         <v>4</v>
       </c>
       <c r="I61" s="22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J61" s="22" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="22" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B62" s="22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C62" s="22" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D62" s="22" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E62" s="22" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F62" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G62" s="22" t="s">
         <v>151</v>
-      </c>
-      <c r="G62" s="22" t="s">
-        <v>150</v>
       </c>
       <c r="H62" s="22" t="n">
         <v>3</v>
       </c>
       <c r="I62" s="22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J62" s="22" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="22" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B63" s="22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C63" s="22" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D63" s="22" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E63" s="22" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F63" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G63" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H63" s="22" t="n">
         <v>3</v>
       </c>
       <c r="I63" s="22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J63" s="22" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="22" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B64" s="22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C64" s="22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D64" s="22" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E64" s="22" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F64" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G64" s="22" t="s">
         <v>151</v>
-      </c>
-      <c r="G64" s="22" t="s">
-        <v>150</v>
       </c>
       <c r="H64" s="22" t="n">
         <v>3</v>
       </c>
       <c r="I64" s="22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J64" s="22" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="22" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B65" s="22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C65" s="22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D65" s="22" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E65" s="22" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F65" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G65" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H65" s="22" t="n">
         <v>3</v>
       </c>
       <c r="I65" s="22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J65" s="22" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="22" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B66" s="22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C66" s="22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D66" s="22" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E66" s="22" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F66" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G66" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H66" s="22" t="n">
         <v>2</v>
       </c>
       <c r="I66" s="22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J66" s="22" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="22" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B67" s="22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C67" s="22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D67" s="22" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E67" s="22" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F67" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G67" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H67" s="22" t="n">
         <v>2</v>
       </c>
       <c r="I67" s="22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J67" s="22" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="22" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B68" s="22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C68" s="22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D68" s="22" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="E68" s="22" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F68" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G68" s="22" t="s">
         <v>151</v>
-      </c>
-      <c r="G68" s="22" t="s">
-        <v>150</v>
       </c>
       <c r="H68" s="22" t="n">
         <v>2</v>
       </c>
       <c r="I68" s="22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J68" s="22" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="22" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B69" s="22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C69" s="22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D69" s="22" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E69" s="22" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F69" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G69" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H69" s="22" t="n">
         <v>4</v>
       </c>
       <c r="I69" s="22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J69" s="22" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="22" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B70" s="22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C70" s="22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D70" s="22" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E70" s="22" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F70" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G70" s="22" t="s">
         <v>151</v>
-      </c>
-      <c r="G70" s="22" t="s">
-        <v>150</v>
       </c>
       <c r="H70" s="22" t="n">
         <v>3</v>
       </c>
       <c r="I70" s="22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J70" s="22" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="22" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B71" s="22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C71" s="22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D71" s="22" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="E71" s="22" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F71" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G71" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H71" s="22" t="n">
         <v>1</v>
       </c>
       <c r="I71" s="22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J71" s="22" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="22" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B72" s="22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C72" s="22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D72" s="22" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E72" s="22" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F72" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G72" s="22" t="s">
         <v>151</v>
-      </c>
-      <c r="G72" s="22" t="s">
-        <v>150</v>
       </c>
       <c r="H72" s="22" t="n">
         <v>1</v>
       </c>
       <c r="I72" s="22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J72" s="22" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="22" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B73" s="22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C73" s="22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D73" s="22" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E73" s="22" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F73" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G73" s="22" t="s">
         <v>151</v>
-      </c>
-      <c r="G73" s="22" t="s">
-        <v>150</v>
       </c>
       <c r="H73" s="22" t="n">
         <v>1</v>
       </c>
       <c r="I73" s="22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J73" s="22" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -33544,135 +33464,135 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="80"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="80"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="21" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="22" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="22" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="22" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="22" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="22" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="22" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="22" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="22" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="22" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="22" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="22" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="22" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="22" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -33692,44 +33612,44 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F57"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="90"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="90"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B4" s="21" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33743,13 +33663,13 @@
         <v>1</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33763,13 +33683,13 @@
         <v>2</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33783,13 +33703,13 @@
         <v>3</v>
       </c>
       <c r="D7" s="22" t="s">
+        <v>379</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>378</v>
+      </c>
+      <c r="F7" s="22" t="s">
         <v>376</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>375</v>
-      </c>
-      <c r="F7" s="22" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33803,13 +33723,13 @@
         <v>4</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33823,10 +33743,10 @@
         <v>1</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F9" s="22"/>
     </row>
@@ -33841,13 +33761,13 @@
         <v>2</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33861,10 +33781,10 @@
         <v>3</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="F11" s="22"/>
     </row>
@@ -33879,13 +33799,13 @@
         <v>4</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33899,10 +33819,10 @@
         <v>5</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F13" s="22"/>
     </row>
@@ -33917,13 +33837,13 @@
         <v>6</v>
       </c>
       <c r="D14" s="22" t="s">
+        <v>387</v>
+      </c>
+      <c r="E14" s="22" t="s">
         <v>384</v>
       </c>
-      <c r="E14" s="22" t="s">
-        <v>381</v>
-      </c>
       <c r="F14" s="22" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33937,13 +33857,13 @@
         <v>7</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33957,13 +33877,13 @@
         <v>1</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33977,13 +33897,13 @@
         <v>2</v>
       </c>
       <c r="D17" s="26" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33997,13 +33917,13 @@
         <v>3</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="E18" s="22" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34017,13 +33937,13 @@
         <v>4</v>
       </c>
       <c r="D19" s="22" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E19" s="22" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F19" s="22" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34037,13 +33957,13 @@
         <v>1</v>
       </c>
       <c r="D20" s="22" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="E20" s="22" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="F20" s="22" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34057,13 +33977,13 @@
         <v>2</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34077,13 +33997,13 @@
         <v>3</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E22" s="22" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="F22" s="22" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34097,13 +34017,13 @@
         <v>4</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="E23" s="22" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="F23" s="22" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34117,13 +34037,13 @@
         <v>5</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="E24" s="22" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="F24" s="22" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34137,13 +34057,13 @@
         <v>6</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E25" s="22" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="F25" s="22" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34157,13 +34077,13 @@
         <v>1</v>
       </c>
       <c r="D26" s="22" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="E26" s="22" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F26" s="22" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34177,13 +34097,13 @@
         <v>2</v>
       </c>
       <c r="D27" s="22" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F27" s="22" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34197,13 +34117,13 @@
         <v>3</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34217,13 +34137,13 @@
         <v>1</v>
       </c>
       <c r="D29" s="22" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F29" s="22" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34237,13 +34157,13 @@
         <v>2</v>
       </c>
       <c r="D30" s="22" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="E30" s="22" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F30" s="22" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34257,10 +34177,10 @@
         <v>1</v>
       </c>
       <c r="D31" s="22" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="E31" s="22" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F31" s="22"/>
     </row>
@@ -34275,10 +34195,10 @@
         <v>2</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="E32" s="22" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="F32" s="22"/>
     </row>
@@ -34293,10 +34213,10 @@
         <v>3</v>
       </c>
       <c r="D33" s="22" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E33" s="22" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="F33" s="22"/>
     </row>
@@ -34311,10 +34231,10 @@
         <v>1</v>
       </c>
       <c r="D34" s="22" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E34" s="22" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F34" s="22"/>
     </row>
@@ -34329,13 +34249,13 @@
         <v>2</v>
       </c>
       <c r="D35" s="22" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E35" s="22" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F35" s="22" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34349,13 +34269,13 @@
         <v>3</v>
       </c>
       <c r="D36" s="22" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E36" s="22" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F36" s="22" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34369,10 +34289,10 @@
         <v>1</v>
       </c>
       <c r="D37" s="22" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E37" s="22" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F37" s="22"/>
     </row>
@@ -34387,10 +34307,10 @@
         <v>2</v>
       </c>
       <c r="D38" s="22" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="E38" s="22" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="F38" s="22"/>
     </row>
@@ -34405,10 +34325,10 @@
         <v>1</v>
       </c>
       <c r="D39" s="22" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E39" s="22" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F39" s="22"/>
     </row>
@@ -34423,323 +34343,323 @@
         <v>2</v>
       </c>
       <c r="D40" s="26" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="E40" s="22" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="F40" s="22" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B41" s="22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C41" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D41" s="22" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E41" s="22" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F41" s="22" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B42" s="22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C42" s="22" t="n">
         <v>2</v>
       </c>
       <c r="D42" s="22" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="E42" s="22" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F42" s="22" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B43" s="22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C43" s="22" t="n">
         <v>3</v>
       </c>
       <c r="D43" s="22" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F43" s="22" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B44" s="22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C44" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D44" s="22" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="E44" s="22" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F44" s="22" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B45" s="22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C45" s="22" t="n">
         <v>2</v>
       </c>
       <c r="D45" s="22" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F45" s="22" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B46" s="22" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C46" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D46" s="22" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E46" s="22" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F46" s="22" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B47" s="22" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C47" s="22" t="n">
         <v>2</v>
       </c>
       <c r="D47" s="22" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="E47" s="22" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F47" s="22"/>
     </row>
     <row r="48" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="22" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B48" s="22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C48" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D48" s="22" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="E48" s="22" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F48" s="22"/>
     </row>
     <row r="49" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="22" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B49" s="22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C49" s="22" t="n">
         <v>2</v>
       </c>
       <c r="D49" s="22" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="E49" s="22" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F49" s="22"/>
     </row>
     <row r="50" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="22" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B50" s="22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C50" s="22" t="n">
         <v>3</v>
       </c>
       <c r="D50" s="22" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E50" s="22" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="F50" s="22"/>
     </row>
     <row r="51" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B51" s="22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C51" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D51" s="22" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="E51" s="22" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F51" s="22" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B52" s="22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C52" s="22" t="n">
         <v>2</v>
       </c>
       <c r="D52" s="22" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="E52" s="22" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="F52" s="22"/>
     </row>
     <row r="53" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B53" s="22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C53" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D53" s="22" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E53" s="22" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F53" s="22"/>
     </row>
     <row r="54" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B54" s="22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C54" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D54" s="22" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="E54" s="22"/>
       <c r="F54" s="22"/>
     </row>
     <row r="55" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="22" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B55" s="22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C55" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D55" s="22" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="E55" s="22"/>
       <c r="F55" s="22"/>
     </row>
     <row r="56" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="22" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B56" s="22" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C56" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D56" s="22" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="E56" s="22"/>
       <c r="F56" s="22"/>
     </row>
     <row r="57" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="22" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B57" s="22" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C57" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D57" s="22" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="E57" s="22"/>
       <c r="F57" s="22"/>
@@ -34761,37 +34681,37 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L24"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="70"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="6" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="6" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="1" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D4" s="21" t="s">
         <v>4</v>
@@ -34799,119 +34719,119 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="22" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="22" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="22" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B7" s="27" t="n">
         <v>51</v>
       </c>
       <c r="C7" s="22" t="s">
+        <v>452</v>
+      </c>
+      <c r="D7" s="22" t="s">
         <v>449</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="22" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B8" s="27" t="n">
         <v>10</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="22" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B9" s="27" t="n">
         <v>45</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="22" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B10" s="27" t="n">
         <v>40</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="22" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B11" s="27" t="n">
         <v>5</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="22" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="B13" s="27" t="n">
         <f aca="false">SUM(B8:B11)</f>
@@ -34922,55 +34842,55 @@
         <v>OK</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="28" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="G16" s="21" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="H16" s="21" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="I16" s="21" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="J16" s="21" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K16" s="21" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="L16" s="21" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="22" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B17" s="27" t="n">
         <v>80</v>
@@ -35015,7 +34935,7 @@
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="22" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B18" s="27" t="n">
         <v>100</v>
@@ -35060,7 +34980,7 @@
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="22" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B19" s="27" t="n">
         <v>80</v>
@@ -35105,7 +35025,7 @@
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="22" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B20" s="27" t="n">
         <v>100</v>
@@ -35150,7 +35070,7 @@
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="22" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B21" s="27" t="n">
         <v>1</v>
@@ -35195,7 +35115,7 @@
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="25" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B23" s="25"/>
       <c r="C23" s="25"/>
@@ -35209,7 +35129,7 @@
       <c r="K23" s="25"/>
       <c r="L23" s="25"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="25"/>
       <c r="B24" s="25"/>
       <c r="C24" s="25"/>
@@ -35243,34 +35163,34 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="55"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="21" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35278,16 +35198,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E4" s="22" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35295,16 +35215,16 @@
         <v>2</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35312,16 +35232,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35329,16 +35249,16 @@
         <v>4</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35346,16 +35266,16 @@
         <v>5</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35363,16 +35283,16 @@
         <v>6</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35380,16 +35300,16 @@
         <v>7</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35397,16 +35317,16 @@
         <v>8</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35414,16 +35334,16 @@
         <v>9</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35431,16 +35351,16 @@
         <v>10</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35448,16 +35368,16 @@
         <v>11</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35465,16 +35385,16 @@
         <v>12</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35482,16 +35402,16 @@
         <v>13</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35499,16 +35419,16 @@
         <v>14</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35516,16 +35436,16 @@
         <v>15</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E18" s="22" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35533,16 +35453,16 @@
         <v>16</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D19" s="22" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E19" s="22" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35550,16 +35470,16 @@
         <v>17</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D20" s="22" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E20" s="22" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35567,16 +35487,16 @@
         <v>18</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
   </sheetData>
@@ -35596,7 +35516,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="14.4453125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.4453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="1.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="27.71"/>
@@ -35609,7 +35529,7 @@
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2"/>
       <c r="B1" s="3" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -35695,10 +35615,10 @@
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2"/>
       <c r="B4" s="29" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -35730,7 +35650,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -35762,7 +35682,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="30" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -35794,7 +35714,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="30" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -35826,7 +35746,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="30" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -35858,7 +35778,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -35887,10 +35807,10 @@
     <row r="10" customFormat="false" ht="50.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2"/>
       <c r="B10" s="30" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C10" s="30" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -35922,7 +35842,7 @@
         <v>7</v>
       </c>
       <c r="C11" s="30" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -35954,7 +35874,7 @@
         <v>8</v>
       </c>
       <c r="C12" s="30" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -35986,7 +35906,7 @@
         <v>9</v>
       </c>
       <c r="C13" s="30" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -36018,7 +35938,7 @@
         <v>10</v>
       </c>
       <c r="C14" s="30" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
